--- a/ConvertToExcel/mau_chuan.xlsx
+++ b/ConvertToExcel/mau_chuan.xlsx
@@ -31,9 +31,6 @@
     <t>?title</t>
   </si>
   <si>
-    <t>#?h_tu_ngay + + !2.tu_ngay + + ?h_den_ngay + + !2.den_ngay</t>
-  </si>
-  <si>
     <t>?h_stt</t>
   </si>
   <si>
@@ -53,6 +50,9 @@
   </si>
   <si>
     <t>?chiefAccountantName</t>
+  </si>
+  <si>
+    <t>#?h_tu_ngay + + !1.tu_ngay + + ?h_den_ngay + + !1.den_ngay</t>
   </si>
 </sst>
 </file>
@@ -62,7 +62,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="####"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,40 +75,46 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -165,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -185,17 +191,18 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,152 +506,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="7"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="20.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:13" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
         <v>8</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="9" t="s">
-        <v>9</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -652,27 +662,27 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:13">
-      <c r="B14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="H14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -683,9 +693,9 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -697,12 +707,10 @@
       <c r="J16" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A6:I6"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="H13:J13"/>
